--- a/12621579.xlsx
+++ b/12621579.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aayus\Downloads\Demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{71084F41-3875-4446-950B-8C8DC28F9D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA7886B-ED95-4612-A82E-30FCC35824BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -228,6 +227,9 @@
   </si>
   <si>
     <t>Feeling better</t>
+  </si>
+  <si>
+    <t>CA of Python</t>
   </si>
 </sst>
 </file>
@@ -1993,26 +1995,50 @@
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>0</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <v>200</v>
+      </c>
+      <c r="G28" s="14">
+        <v>4</v>
+      </c>
+      <c r="H28" s="14">
+        <v>180</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/12621579.xlsx
+++ b/12621579.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aayus\Downloads\Demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA7886B-ED95-4612-A82E-30FCC35824BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3195994F-9F89-44F3-835A-71F318993C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4644" yWindow="2184" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2041,47 +2041,91 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B29" s="14">
+        <v>360</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>240</v>
+      </c>
+      <c r="E29" s="14">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>400</v>
+      </c>
+      <c r="G29" s="14">
+        <v>8</v>
+      </c>
+      <c r="H29" s="14">
+        <v>120</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
+        <v>320</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B30" s="14">
+        <v>300</v>
+      </c>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <v>360</v>
+      </c>
+      <c r="E30" s="14">
+        <v>0</v>
+      </c>
+      <c r="F30" s="14">
+        <v>150</v>
+      </c>
+      <c r="G30" s="14">
+        <v>3</v>
+      </c>
+      <c r="H30" s="14">
+        <v>150</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
+        <v>480</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">

--- a/12621579.xlsx
+++ b/12621579.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aayus\Downloads\Demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3195994F-9F89-44F3-835A-71F318993C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091B9551-B1DA-4FA7-83A7-2AA39B78D473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4644" yWindow="2184" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -142,42 +142,6 @@
     <t>Date</t>
   </si>
   <si>
-    <t>Sleep (min)</t>
-  </si>
-  <si>
-    <t>Fitness (min)</t>
-  </si>
-  <si>
-    <t>Study (min)</t>
-  </si>
-  <si>
-    <t>Coding (min)</t>
-  </si>
-  <si>
-    <t>Class (min)</t>
-  </si>
-  <si>
-    <t>Classes Attended</t>
-  </si>
-  <si>
-    <t>Other Activities (min)</t>
-  </si>
-  <si>
-    <t>Total Tracked (min)</t>
-  </si>
-  <si>
-    <t>Free/Unaccounted (min)</t>
-  </si>
-  <si>
-    <t>Day's Feeling</t>
-  </si>
-  <si>
-    <t>Satisfaction Level</t>
-  </si>
-  <si>
-    <t>Energy Level</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -230,6 +194,42 @@
   </si>
   <si>
     <t>CA of Python</t>
+  </si>
+  <si>
+    <t>Sleep_min</t>
+  </si>
+  <si>
+    <t>Fitness_min</t>
+  </si>
+  <si>
+    <t>Study_min</t>
+  </si>
+  <si>
+    <t>Coding_min</t>
+  </si>
+  <si>
+    <t>Class_min</t>
+  </si>
+  <si>
+    <t>Classes_Attended</t>
+  </si>
+  <si>
+    <t>Other_Activities_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total_Tracked </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free/Unaccounted </t>
+  </si>
+  <si>
+    <t>Day's_Feeling</t>
+  </si>
+  <si>
+    <t>Satisfaction_Level</t>
+  </si>
+  <si>
+    <t>Energy_Level</t>
   </si>
 </sst>
 </file>
@@ -847,7 +847,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
@@ -917,7 +917,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
@@ -934,7 +934,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -962,48 +962,48 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
     </row>
-    <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="N5" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1040,16 +1040,16 @@
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1086,16 +1086,16 @@
         <v>610</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1132,16 +1132,16 @@
         <v>250</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1178,16 +1178,16 @@
         <v>700</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1224,16 +1224,16 @@
         <v>365</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1270,16 +1270,16 @@
         <v>540</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1316,16 +1316,16 @@
         <v>675</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1362,13 +1362,13 @@
         <v>540</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N13" s="17"/>
     </row>
@@ -1406,13 +1406,13 @@
         <v>550</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N14" s="17"/>
     </row>
@@ -1450,13 +1450,13 @@
         <v>305</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="N15" s="17"/>
     </row>
@@ -1494,13 +1494,13 @@
         <v>430</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N16" s="17"/>
     </row>
@@ -1538,13 +1538,13 @@
         <v>500</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N17" s="17"/>
     </row>
@@ -1582,13 +1582,13 @@
         <v>435</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N18" s="17"/>
     </row>
@@ -1626,13 +1626,13 @@
         <v>450</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N19" s="17"/>
     </row>
@@ -1670,13 +1670,13 @@
         <v>480</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N20" s="17"/>
     </row>
@@ -1714,13 +1714,13 @@
         <v>610</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N21" s="17"/>
     </row>
@@ -1758,13 +1758,13 @@
         <v>500</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N22" s="17"/>
     </row>
@@ -1802,16 +1802,16 @@
         <v>435</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1848,16 +1848,16 @@
         <v>750</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -1894,16 +1894,16 @@
         <v>660</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -1940,13 +1940,13 @@
         <v>480</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N26" s="17"/>
     </row>
@@ -1984,13 +1984,13 @@
         <v>480</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N27" s="17"/>
     </row>
@@ -2028,16 +2028,16 @@
         <v>640</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2074,13 +2074,13 @@
         <v>320</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N29" s="17"/>
     </row>
@@ -2118,124 +2118,234 @@
         <v>480</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B31" s="14">
+        <v>360</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>180</v>
+      </c>
+      <c r="E31" s="14">
+        <v>45</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>240</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1075</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
+        <v>365</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>240</v>
+      </c>
+      <c r="E32" s="14">
+        <v>60</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>180</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
+        <v>540</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B33" s="14">
+        <v>300</v>
+      </c>
+      <c r="C33" s="14">
+        <v>0</v>
+      </c>
+      <c r="D33" s="14">
+        <v>300</v>
+      </c>
+      <c r="E33" s="14">
+        <v>60</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>240</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
+        <v>540</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>47</v>
+      </c>
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B34" s="14">
+        <v>360</v>
+      </c>
+      <c r="C34" s="14">
+        <v>0</v>
+      </c>
+      <c r="D34" s="14">
+        <v>240</v>
+      </c>
+      <c r="E34" s="14">
+        <v>0</v>
+      </c>
+      <c r="F34" s="14">
+        <v>200</v>
+      </c>
+      <c r="G34" s="14">
+        <v>4</v>
+      </c>
+      <c r="H34" s="14">
+        <v>180</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
+        <v>460</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B35" s="14">
+        <v>300</v>
+      </c>
+      <c r="C35" s="14">
+        <v>0</v>
+      </c>
+      <c r="D35" s="14">
+        <v>180</v>
+      </c>
+      <c r="E35" s="14">
+        <v>0</v>
+      </c>
+      <c r="F35" s="14">
+        <v>200</v>
+      </c>
+      <c r="G35" s="14">
+        <v>4</v>
+      </c>
+      <c r="H35" s="14">
+        <v>150</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">

--- a/12621579.xlsx
+++ b/12621579.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aayus\Downloads\Demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091B9551-B1DA-4FA7-83A7-2AA39B78D473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3A303A-A029-4696-9002-19CD48BEC5F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2349,47 +2349,91 @@
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B36" s="14">
+        <v>360</v>
+      </c>
+      <c r="C36" s="14">
+        <v>0</v>
+      </c>
+      <c r="D36" s="14">
+        <v>240</v>
+      </c>
+      <c r="E36" s="14">
+        <v>45</v>
+      </c>
+      <c r="F36" s="14">
+        <v>400</v>
+      </c>
+      <c r="G36" s="14">
+        <v>8</v>
+      </c>
+      <c r="H36" s="14">
+        <v>120</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1165</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
+        <v>275</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>47</v>
+      </c>
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B37" s="14">
+        <v>420</v>
+      </c>
+      <c r="C37" s="14">
+        <v>0</v>
+      </c>
+      <c r="D37" s="14">
+        <v>210</v>
+      </c>
+      <c r="E37" s="14">
+        <v>60</v>
+      </c>
+      <c r="F37" s="14">
+        <v>150</v>
+      </c>
+      <c r="G37" s="14">
+        <v>3</v>
+      </c>
+      <c r="H37" s="14">
+        <v>240</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
+        <v>360</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
